--- a/survey/impact_survey_xlsform.xlsx
+++ b/survey/impact_survey_xlsform.xlsx
@@ -436,8 +436,8 @@
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
@@ -522,7 +522,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Portfolio demonstration only</t>
+          <t>Synthetic dataset only; do not enter real personal information</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Do you agree to continue with this fictional practice survey?</t>
+          <t>Do you agree to continue with this synthetic survey?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2492,7 +2492,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Impact Survey Data Quality Toolkit - Synthetic Practice Survey</t>
+          <t>Impact Survey Data Quality Toolkit - Synthetic Training Follow-up Survey</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
